--- a/datos_ventas.xlsx
+++ b/datos_ventas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alejandrogarciaruiz/Desktop/FundamentosML/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{100D8D4C-2B04-C347-9E11-234F4C664CE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{424EFD0C-A12A-CA43-A2B5-8439BF62BFCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="400" yWindow="520" windowWidth="25440" windowHeight="14860" xr2:uid="{5EF2C60A-65E9-B24D-B7AE-16CE341DB1BD}"/>
+    <workbookView xWindow="4520" yWindow="660" windowWidth="25440" windowHeight="14860" xr2:uid="{5EF2C60A-65E9-B24D-B7AE-16CE341DB1BD}"/>
   </bookViews>
   <sheets>
     <sheet name="datos_ventas" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="21">
   <si>
     <t>Ventas</t>
   </si>
@@ -75,6 +75,27 @@
   </si>
   <si>
     <t>Distancia</t>
+  </si>
+  <si>
+    <t>3.- Obtener K</t>
+  </si>
+  <si>
+    <t>De manera clasica, K se obtiene a través de la raíz cuadrada de N</t>
+  </si>
+  <si>
+    <t>N = 100</t>
+  </si>
+  <si>
+    <t>K =</t>
+  </si>
+  <si>
+    <t>4.- La clase que asigna el algoritmo es la clase MODA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Para este ejemplo es: </t>
+  </si>
+  <si>
+    <t>scikit-learn</t>
   </si>
 </sst>
 </file>
@@ -217,7 +238,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -397,12 +418,6 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="10">
     <border>
@@ -564,15 +579,16 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2533,10 +2549,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA70870B-24DD-004A-99CB-2FBD834C4939}">
-  <dimension ref="A1:AB101"/>
+  <dimension ref="A1:AE101"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -2570,8 +2586,11 @@
       <c r="AB1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AE1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2595,22 +2614,28 @@
       </c>
       <c r="W2">
         <f>SQRT(POWER(L$8-B2,2)+POWER(M$8-C2,2))</f>
-        <v>0</v>
+        <v>11.180339887498949</v>
       </c>
       <c r="X2">
         <v>0</v>
       </c>
-      <c r="Z2">
-        <v>1</v>
-      </c>
-      <c r="AA2">
-        <v>0</v>
-      </c>
-      <c r="AB2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z2" s="3">
+        <v>14</v>
+      </c>
+      <c r="AA2" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB2" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="4">
+        <v>1</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2628,22 +2653,25 @@
       </c>
       <c r="W3">
         <f>SQRT(POWER(L$8-B3,2)+POWER(M$8-C3,2))</f>
-        <v>7.6157731058639087</v>
+        <v>3.6055512754639891</v>
       </c>
       <c r="X3">
         <v>0</v>
       </c>
-      <c r="Z3">
-        <v>3</v>
-      </c>
-      <c r="AA3">
-        <v>0</v>
-      </c>
-      <c r="AB3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z3" s="3">
+        <v>17</v>
+      </c>
+      <c r="AA3" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2659,7 +2687,7 @@
       <c r="L4" t="s">
         <v>5</v>
       </c>
-      <c r="P4" s="3" t="s">
+      <c r="P4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="V4">
@@ -2667,22 +2695,28 @@
       </c>
       <c r="W4">
         <f>SQRT(POWER(L$8-B4,2)+POWER(M$8-C4,2))</f>
-        <v>0</v>
+        <v>11.180339887498949</v>
       </c>
       <c r="X4">
         <v>0</v>
       </c>
-      <c r="Z4">
-        <v>22</v>
-      </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z4" s="3">
+        <v>46</v>
+      </c>
+      <c r="AA4" s="3">
+        <v>1</v>
+      </c>
+      <c r="AB4" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="4">
+        <v>3</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2700,22 +2734,28 @@
       </c>
       <c r="W5">
         <f>SQRT(POWER(L$8-B5,2)+POWER(M$8-C5,2))</f>
-        <v>9.2195444572928871</v>
+        <v>3.1622776601683795</v>
       </c>
       <c r="X5">
         <v>0</v>
       </c>
-      <c r="Z5">
-        <v>6</v>
-      </c>
-      <c r="AA5">
-        <v>2.2360679774997898</v>
-      </c>
-      <c r="AB5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z5" s="3">
+        <v>40</v>
+      </c>
+      <c r="AA5" s="3">
+        <v>1.4142135623730951</v>
+      </c>
+      <c r="AB5" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="4">
+        <v>4</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2739,22 +2779,29 @@
       </c>
       <c r="W6">
         <f>SQRT(POWER(L$8-B6,2)+POWER(M$8-C6,2))</f>
-        <v>4.4721359549995796</v>
+        <v>6.7082039324993694</v>
       </c>
       <c r="X6">
         <v>0</v>
       </c>
-      <c r="Z6">
-        <v>29</v>
-      </c>
-      <c r="AA6">
-        <v>2.2360679774997898</v>
-      </c>
-      <c r="AB6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z6" s="3">
+        <v>16</v>
+      </c>
+      <c r="AA6" s="3">
+        <v>2</v>
+      </c>
+      <c r="AB6" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="4">
+        <v>5</v>
+      </c>
+      <c r="AE6">
+        <f>SQRT(100)</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2781,22 +2828,25 @@
       </c>
       <c r="W7">
         <f>SQRT(POWER(L$8-B7,2)+POWER(M$8-C7,2))</f>
+        <v>10</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="3">
+        <v>31</v>
+      </c>
+      <c r="AA7" s="3">
         <v>2.2360679774997898</v>
       </c>
-      <c r="X7">
-        <v>0</v>
-      </c>
-      <c r="Z7">
-        <v>21</v>
-      </c>
-      <c r="AA7">
-        <v>3</v>
-      </c>
-      <c r="AB7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AB7" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2810,12 +2860,12 @@
         <v>0</v>
       </c>
       <c r="L8" s="1">
-        <v>-9</v>
+        <v>-4</v>
       </c>
       <c r="M8" s="1">
-        <v>0</v>
-      </c>
-      <c r="N8" s="2">
+        <v>10</v>
+      </c>
+      <c r="N8" s="1">
         <v>0</v>
       </c>
       <c r="V8">
@@ -2823,22 +2873,25 @@
       </c>
       <c r="W8">
         <f>SQRT(POWER(L$8-B8,2)+POWER(M$8-C8,2))</f>
-        <v>12.041594578792296</v>
+        <v>4.4721359549995796</v>
       </c>
       <c r="X8">
         <v>0</v>
       </c>
-      <c r="Z8">
-        <v>11</v>
-      </c>
-      <c r="AA8">
-        <v>3.6055512754639891</v>
-      </c>
-      <c r="AB8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3">
+        <v>39</v>
+      </c>
+      <c r="AA8" s="3">
+        <v>2.2360679774997898</v>
+      </c>
+      <c r="AB8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2856,22 +2909,28 @@
       </c>
       <c r="W9">
         <f>SQRT(POWER(L$8-B9,2)+POWER(M$8-C9,2))</f>
-        <v>5.3851648071345037</v>
+        <v>5.8309518948453007</v>
       </c>
       <c r="X9">
         <v>0</v>
       </c>
-      <c r="Z9">
-        <v>19</v>
-      </c>
-      <c r="AA9">
-        <v>3.6055512754639891</v>
-      </c>
-      <c r="AB9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3">
+        <v>15</v>
+      </c>
+      <c r="AA9" s="3">
+        <v>3</v>
+      </c>
+      <c r="AB9" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="4">
+        <v>8</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2889,22 +2948,25 @@
       </c>
       <c r="W10">
         <f>SQRT(POWER(L$8-B10,2)+POWER(M$8-C10,2))</f>
-        <v>8.5440037453175304</v>
+        <v>7.6157731058639087</v>
       </c>
       <c r="X10">
         <v>0</v>
       </c>
-      <c r="Z10">
-        <v>10</v>
-      </c>
-      <c r="AA10">
-        <v>4</v>
-      </c>
-      <c r="AB10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3">
+        <v>50</v>
+      </c>
+      <c r="AA10" s="3">
+        <v>3</v>
+      </c>
+      <c r="AB10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2922,22 +2984,28 @@
       </c>
       <c r="W11">
         <f>SQRT(POWER(L$8-B11,2)+POWER(M$8-C11,2))</f>
+        <v>10.04987562112089</v>
+      </c>
+      <c r="X11">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="3">
         <v>4</v>
       </c>
-      <c r="X11">
-        <v>0</v>
-      </c>
-      <c r="Z11">
-        <v>33</v>
-      </c>
-      <c r="AA11">
-        <v>4.2426406871192848</v>
-      </c>
-      <c r="AB11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3">
+        <v>3.1622776601683795</v>
+      </c>
+      <c r="AB11" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="4">
+        <v>10</v>
+      </c>
+      <c r="AE11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2955,22 +3023,26 @@
       </c>
       <c r="W12">
         <f>SQRT(POWER(L$8-B12,2)+POWER(M$8-C12,2))</f>
-        <v>3.6055512754639891</v>
+        <v>8.2462112512353212</v>
       </c>
       <c r="X12">
         <v>0</v>
       </c>
-      <c r="Z12">
-        <v>5</v>
-      </c>
-      <c r="AA12">
-        <v>4.4721359549995796</v>
-      </c>
-      <c r="AB12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3">
+        <v>20</v>
+      </c>
+      <c r="AA12" s="3">
+        <v>3.1622776601683795</v>
+      </c>
+      <c r="AB12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="3"/>
+      <c r="AE12" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2988,22 +3060,23 @@
       </c>
       <c r="W13">
         <f>SQRT(POWER(L$8-B13,2)+POWER(M$8-C13,2))</f>
-        <v>5</v>
+        <v>7.0710678118654755</v>
       </c>
       <c r="X13">
         <v>0</v>
       </c>
-      <c r="Z13">
-        <v>18</v>
-      </c>
-      <c r="AA13">
-        <v>4.4721359549995796</v>
-      </c>
-      <c r="AB13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>2</v>
+      </c>
+      <c r="AA13" s="3">
+        <v>3.6055512754639891</v>
+      </c>
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="3"/>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -3021,22 +3094,23 @@
       </c>
       <c r="W14">
         <f>SQRT(POWER(L$8-B14,2)+POWER(M$8-C14,2))</f>
-        <v>6.7082039324993694</v>
+        <v>4.4721359549995796</v>
       </c>
       <c r="X14">
         <v>0</v>
       </c>
-      <c r="Z14">
-        <v>35</v>
-      </c>
-      <c r="AA14">
-        <v>4.4721359549995796</v>
-      </c>
-      <c r="AB14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>37</v>
+      </c>
+      <c r="AA14" s="3">
+        <v>3.6055512754639891</v>
+      </c>
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3"/>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -3054,22 +3128,23 @@
       </c>
       <c r="W15">
         <f>SQRT(POWER(L$8-B15,2)+POWER(M$8-C15,2))</f>
-        <v>11.180339887498949</v>
+        <v>0</v>
       </c>
       <c r="X15">
         <v>0</v>
       </c>
-      <c r="Z15">
-        <v>12</v>
-      </c>
-      <c r="AA15">
-        <v>5</v>
-      </c>
-      <c r="AB15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>45</v>
+      </c>
+      <c r="AA15" s="3">
+        <v>3.6055512754639891</v>
+      </c>
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="3"/>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
@@ -3090,22 +3165,26 @@
       </c>
       <c r="W16">
         <f>SQRT(POWER(L$8-B16,2)+POWER(M$8-C16,2))</f>
-        <v>8.6023252670426267</v>
+        <v>3</v>
       </c>
       <c r="X16">
         <v>0</v>
       </c>
-      <c r="Z16">
-        <v>25</v>
-      </c>
-      <c r="AA16">
-        <v>5.0990195135927845</v>
-      </c>
-      <c r="AB16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3">
+        <v>44</v>
+      </c>
+      <c r="AA16" s="3">
+        <v>4.1231056256176606</v>
+      </c>
+      <c r="AB16" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="3"/>
+      <c r="AE16" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
@@ -3123,22 +3202,23 @@
       </c>
       <c r="W17">
         <f>SQRT(POWER(L$8-B17,2)+POWER(M$8-C17,2))</f>
-        <v>12.206555615733702</v>
+        <v>2</v>
       </c>
       <c r="X17">
         <v>0</v>
       </c>
-      <c r="Z17">
-        <v>8</v>
-      </c>
-      <c r="AA17">
-        <v>5.3851648071345037</v>
-      </c>
-      <c r="AB17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z17" s="3">
+        <v>42</v>
+      </c>
+      <c r="AA17" s="3">
+        <v>4.2426406871192848</v>
+      </c>
+      <c r="AB17" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC17" s="3"/>
+    </row>
+    <row r="18" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
@@ -3156,22 +3236,23 @@
       </c>
       <c r="W18">
         <f>SQRT(POWER(L$8-B18,2)+POWER(M$8-C18,2))</f>
-        <v>11.180339887498949</v>
+        <v>0</v>
       </c>
       <c r="X18">
         <v>0</v>
       </c>
-      <c r="Z18">
-        <v>47</v>
-      </c>
-      <c r="AA18">
-        <v>5.3851648071345037</v>
-      </c>
-      <c r="AB18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z18" s="3">
+        <v>7</v>
+      </c>
+      <c r="AA18" s="3">
+        <v>4.4721359549995796</v>
+      </c>
+      <c r="AB18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC18" s="3"/>
+    </row>
+    <row r="19" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
@@ -3189,22 +3270,23 @@
       </c>
       <c r="W19">
         <f>SQRT(POWER(L$8-B19,2)+POWER(M$8-C19,2))</f>
+        <v>8.0622577482985491</v>
+      </c>
+      <c r="X19">
+        <v>0</v>
+      </c>
+      <c r="Z19" s="3">
+        <v>13</v>
+      </c>
+      <c r="AA19" s="3">
         <v>4.4721359549995796</v>
       </c>
-      <c r="X19">
-        <v>0</v>
-      </c>
-      <c r="Z19">
-        <v>23</v>
-      </c>
-      <c r="AA19">
-        <v>6.324555320336759</v>
-      </c>
-      <c r="AB19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
@@ -3222,22 +3304,23 @@
       </c>
       <c r="W20">
         <f>SQRT(POWER(L$8-B20,2)+POWER(M$8-C20,2))</f>
-        <v>3.6055512754639891</v>
+        <v>7.6157731058639087</v>
       </c>
       <c r="X20">
         <v>0</v>
       </c>
-      <c r="Z20">
+      <c r="Z20" s="3">
         <v>28</v>
       </c>
-      <c r="AA20">
-        <v>6.324555320336759</v>
-      </c>
-      <c r="AB20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3">
+        <v>5</v>
+      </c>
+      <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="3"/>
+    </row>
+    <row r="21" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
@@ -3255,22 +3338,23 @@
       </c>
       <c r="W21">
         <f>SQRT(POWER(L$8-B21,2)+POWER(M$8-C21,2))</f>
-        <v>9.2195444572928871</v>
+        <v>3.1622776601683795</v>
       </c>
       <c r="X21">
         <v>0</v>
       </c>
-      <c r="Z21">
-        <v>13</v>
-      </c>
-      <c r="AA21">
-        <v>6.7082039324993694</v>
-      </c>
-      <c r="AB21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3">
+        <v>36</v>
+      </c>
+      <c r="AA21" s="3">
+        <v>5</v>
+      </c>
+      <c r="AB21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC21" s="3"/>
+    </row>
+    <row r="22" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>21</v>
       </c>
@@ -3288,22 +3372,23 @@
       </c>
       <c r="W22">
         <f>SQRT(POWER(L$8-B22,2)+POWER(M$8-C22,2))</f>
-        <v>3</v>
+        <v>10.198039027185569</v>
       </c>
       <c r="X22">
         <v>0</v>
       </c>
-      <c r="Z22">
-        <v>41</v>
-      </c>
-      <c r="AA22">
-        <v>7.0710678118654755</v>
-      </c>
-      <c r="AB22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3">
+        <v>26</v>
+      </c>
+      <c r="AA22" s="3">
+        <v>5.0990195135927845</v>
+      </c>
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="3"/>
+    </row>
+    <row r="23" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
@@ -3321,22 +3406,23 @@
       </c>
       <c r="W23">
         <f>SQRT(POWER(L$8-B23,2)+POWER(M$8-C23,2))</f>
-        <v>0</v>
+        <v>11.180339887498949</v>
       </c>
       <c r="X23">
         <v>0</v>
       </c>
-      <c r="Z23">
-        <v>49</v>
-      </c>
-      <c r="AA23">
-        <v>7.0710678118654755</v>
-      </c>
-      <c r="AB23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z23" s="3">
+        <v>48</v>
+      </c>
+      <c r="AA23" s="3">
+        <v>5.3851648071345037</v>
+      </c>
+      <c r="AB23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC23" s="3"/>
+    </row>
+    <row r="24" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>23</v>
       </c>
@@ -3354,22 +3440,23 @@
       </c>
       <c r="W24">
         <f>SQRT(POWER(L$8-B24,2)+POWER(M$8-C24,2))</f>
-        <v>6.324555320336759</v>
+        <v>8.0622577482985491</v>
       </c>
       <c r="X24">
         <v>0</v>
       </c>
-      <c r="Z24">
-        <v>24</v>
-      </c>
-      <c r="AA24">
-        <v>7.2111025509279782</v>
-      </c>
-      <c r="AB24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3">
+        <v>8</v>
+      </c>
+      <c r="AA24" s="3">
+        <v>5.8309518948453007</v>
+      </c>
+      <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="3"/>
+    </row>
+    <row r="25" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>24</v>
       </c>
@@ -3387,22 +3474,23 @@
       </c>
       <c r="W25">
         <f>SQRT(POWER(L$8-B25,2)+POWER(M$8-C25,2))</f>
-        <v>7.2111025509279782</v>
+        <v>6.0827625302982193</v>
       </c>
       <c r="X25">
         <v>0</v>
       </c>
-      <c r="Z25">
-        <v>44</v>
-      </c>
-      <c r="AA25">
-        <v>7.2111025509279782</v>
-      </c>
-      <c r="AB25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>24</v>
+      </c>
+      <c r="AA25" s="3">
+        <v>6.0827625302982193</v>
+      </c>
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC25" s="3"/>
+    </row>
+    <row r="26" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>25</v>
       </c>
@@ -3420,22 +3508,23 @@
       </c>
       <c r="W26">
         <f>SQRT(POWER(L$8-B26,2)+POWER(M$8-C26,2))</f>
-        <v>5.0990195135927845</v>
+        <v>6.4031242374328485</v>
       </c>
       <c r="X26">
         <v>0</v>
       </c>
-      <c r="Z26">
-        <v>2</v>
-      </c>
-      <c r="AA26">
-        <v>7.6157731058639087</v>
-      </c>
-      <c r="AB26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3">
+        <v>30</v>
+      </c>
+      <c r="AA26" s="3">
+        <v>6.0827625302982193</v>
+      </c>
+      <c r="AB26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC26" s="3"/>
+    </row>
+    <row r="27" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>26</v>
       </c>
@@ -3453,22 +3542,23 @@
       </c>
       <c r="W27">
         <f>SQRT(POWER(L$8-B27,2)+POWER(M$8-C27,2))</f>
-        <v>7.810249675906654</v>
+        <v>5.0990195135927845</v>
       </c>
       <c r="X27">
         <v>0</v>
       </c>
-      <c r="Z27">
-        <v>32</v>
-      </c>
-      <c r="AA27">
-        <v>7.6157731058639087</v>
-      </c>
-      <c r="AB27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3">
+        <v>27</v>
+      </c>
+      <c r="AA27" s="3">
+        <v>6.324555320336759</v>
+      </c>
+      <c r="AB27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC27" s="3"/>
+    </row>
+    <row r="28" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>27</v>
       </c>
@@ -3486,22 +3576,23 @@
       </c>
       <c r="W28">
         <f>SQRT(POWER(L$8-B28,2)+POWER(M$8-C28,2))</f>
-        <v>8.0622577482985491</v>
+        <v>6.324555320336759</v>
       </c>
       <c r="X28">
         <v>0</v>
       </c>
-      <c r="Z28">
-        <v>43</v>
-      </c>
-      <c r="AA28">
-        <v>7.6157731058639087</v>
-      </c>
-      <c r="AB28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>25</v>
+      </c>
+      <c r="AA28" s="3">
+        <v>6.4031242374328485</v>
+      </c>
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC28" s="3"/>
+    </row>
+    <row r="29" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>28</v>
       </c>
@@ -3519,22 +3610,23 @@
       </c>
       <c r="W29">
         <f>SQRT(POWER(L$8-B29,2)+POWER(M$8-C29,2))</f>
-        <v>6.324555320336759</v>
+        <v>5</v>
       </c>
       <c r="X29">
         <v>0</v>
       </c>
-      <c r="Z29">
-        <v>45</v>
-      </c>
-      <c r="AA29">
-        <v>7.6157731058639087</v>
-      </c>
-      <c r="AB29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>5</v>
+      </c>
+      <c r="AA29" s="3">
+        <v>6.7082039324993694</v>
+      </c>
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="3"/>
+    </row>
+    <row r="30" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>29</v>
       </c>
@@ -3552,22 +3644,23 @@
       </c>
       <c r="W30">
         <f>SQRT(POWER(L$8-B30,2)+POWER(M$8-C30,2))</f>
-        <v>2.2360679774997898</v>
+        <v>9.4868329805051381</v>
       </c>
       <c r="X30">
         <v>0</v>
       </c>
-      <c r="Z30">
-        <v>26</v>
-      </c>
-      <c r="AA30">
-        <v>7.810249675906654</v>
-      </c>
-      <c r="AB30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>35</v>
+      </c>
+      <c r="AA30" s="3">
+        <v>6.7082039324993694</v>
+      </c>
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC30" s="3"/>
+    </row>
+    <row r="31" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>30</v>
       </c>
@@ -3585,22 +3678,23 @@
       </c>
       <c r="W31">
         <f>SQRT(POWER(L$8-B31,2)+POWER(M$8-C31,2))</f>
-        <v>9.0553851381374173</v>
+        <v>6.0827625302982193</v>
       </c>
       <c r="X31">
         <v>0</v>
       </c>
-      <c r="Z31">
-        <v>48</v>
-      </c>
-      <c r="AA31">
-        <v>8</v>
-      </c>
-      <c r="AB31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>12</v>
+      </c>
+      <c r="AA31" s="3">
+        <v>7.0710678118654755</v>
+      </c>
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC31" s="3"/>
+    </row>
+    <row r="32" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>31</v>
       </c>
@@ -3618,22 +3712,23 @@
       </c>
       <c r="W32">
         <f>SQRT(POWER(L$8-B32,2)+POWER(M$8-C32,2))</f>
-        <v>8.9442719099991592</v>
+        <v>2.2360679774997898</v>
       </c>
       <c r="X32">
         <v>0</v>
       </c>
-      <c r="Z32">
-        <v>27</v>
-      </c>
-      <c r="AA32">
-        <v>8.0622577482985491</v>
-      </c>
-      <c r="AB32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3">
+        <v>32</v>
+      </c>
+      <c r="AA32" s="3">
+        <v>7.2801098892805181</v>
+      </c>
+      <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="3"/>
+    </row>
+    <row r="33" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>32</v>
       </c>
@@ -3651,22 +3746,23 @@
       </c>
       <c r="W33">
         <f>SQRT(POWER(L$8-B33,2)+POWER(M$8-C33,2))</f>
-        <v>7.6157731058639087</v>
+        <v>7.2801098892805181</v>
       </c>
       <c r="X33">
         <v>0</v>
       </c>
-      <c r="Z33">
-        <v>38</v>
-      </c>
-      <c r="AA33">
-        <v>8.2462112512353212</v>
-      </c>
-      <c r="AB33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z33" s="3">
+        <v>33</v>
+      </c>
+      <c r="AA33" s="3">
+        <v>7.2801098892805181</v>
+      </c>
+      <c r="AB33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC33" s="3"/>
+    </row>
+    <row r="34" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>33</v>
       </c>
@@ -3684,22 +3780,23 @@
       </c>
       <c r="W34">
         <f>SQRT(POWER(L$8-B34,2)+POWER(M$8-C34,2))</f>
-        <v>4.2426406871192848</v>
+        <v>7.2801098892805181</v>
       </c>
       <c r="X34">
         <v>0</v>
       </c>
-      <c r="Z34">
-        <v>9</v>
-      </c>
-      <c r="AA34">
-        <v>8.5440037453175304</v>
-      </c>
-      <c r="AB34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>43</v>
+      </c>
+      <c r="AA34" s="3">
+        <v>7.2801098892805181</v>
+      </c>
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC34" s="3"/>
+    </row>
+    <row r="35" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>34</v>
       </c>
@@ -3717,22 +3814,23 @@
       </c>
       <c r="W35">
         <f>SQRT(POWER(L$8-B35,2)+POWER(M$8-C35,2))</f>
+        <v>10.770329614269007</v>
+      </c>
+      <c r="X35">
+        <v>0</v>
+      </c>
+      <c r="Z35" s="3">
         <v>9</v>
       </c>
-      <c r="X35">
-        <v>0</v>
-      </c>
-      <c r="Z35">
-        <v>15</v>
-      </c>
-      <c r="AA35">
-        <v>8.6023252670426267</v>
-      </c>
-      <c r="AB35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AA35" s="3">
+        <v>7.6157731058639087</v>
+      </c>
+      <c r="AB35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC35" s="3"/>
+    </row>
+    <row r="36" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>35</v>
       </c>
@@ -3750,22 +3848,23 @@
       </c>
       <c r="W36">
         <f>SQRT(POWER(L$8-B36,2)+POWER(M$8-C36,2))</f>
-        <v>4.4721359549995796</v>
+        <v>6.7082039324993694</v>
       </c>
       <c r="X36">
         <v>0</v>
       </c>
-      <c r="Z36">
-        <v>50</v>
-      </c>
-      <c r="AA36">
-        <v>8.6023252670426267</v>
-      </c>
-      <c r="AB36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z36" s="3">
+        <v>19</v>
+      </c>
+      <c r="AA36" s="3">
+        <v>7.6157731058639087</v>
+      </c>
+      <c r="AB36" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC36" s="3"/>
+    </row>
+    <row r="37" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>36</v>
       </c>
@@ -3783,22 +3882,23 @@
       </c>
       <c r="W37">
         <f>SQRT(POWER(L$8-B37,2)+POWER(M$8-C37,2))</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="X37">
         <v>0</v>
       </c>
-      <c r="Z37">
-        <v>31</v>
-      </c>
-      <c r="AA37">
-        <v>8.9442719099991592</v>
-      </c>
-      <c r="AB37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z37" s="3">
+        <v>47</v>
+      </c>
+      <c r="AA37" s="3">
+        <v>8</v>
+      </c>
+      <c r="AB37" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC37" s="3"/>
+    </row>
+    <row r="38" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>37</v>
       </c>
@@ -3816,22 +3916,23 @@
       </c>
       <c r="W38">
         <f>SQRT(POWER(L$8-B38,2)+POWER(M$8-C38,2))</f>
-        <v>11.313708498984761</v>
+        <v>3.6055512754639891</v>
       </c>
       <c r="X38">
         <v>0</v>
       </c>
-      <c r="Z38">
-        <v>34</v>
-      </c>
-      <c r="AA38">
-        <v>9</v>
-      </c>
-      <c r="AB38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z38" s="3">
+        <v>18</v>
+      </c>
+      <c r="AA38" s="3">
+        <v>8.0622577482985491</v>
+      </c>
+      <c r="AB38" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC38" s="3"/>
+    </row>
+    <row r="39" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>38</v>
       </c>
@@ -3849,22 +3950,23 @@
       </c>
       <c r="W39">
         <f>SQRT(POWER(L$8-B39,2)+POWER(M$8-C39,2))</f>
-        <v>8.2462112512353212</v>
+        <v>8.5440037453175304</v>
       </c>
       <c r="X39">
         <v>0</v>
       </c>
-      <c r="Z39">
-        <v>77</v>
-      </c>
-      <c r="AA39">
-        <v>9</v>
-      </c>
-      <c r="AB39">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3">
+        <v>23</v>
+      </c>
+      <c r="AA39" s="3">
+        <v>8.0622577482985491</v>
+      </c>
+      <c r="AB39" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>39</v>
       </c>
@@ -3882,22 +3984,23 @@
       </c>
       <c r="W40">
         <f>SQRT(POWER(L$8-B40,2)+POWER(M$8-C40,2))</f>
-        <v>9.4868329805051381</v>
+        <v>2.2360679774997898</v>
       </c>
       <c r="X40">
         <v>0</v>
       </c>
-      <c r="Z40">
-        <v>30</v>
-      </c>
-      <c r="AA40">
-        <v>9.0553851381374173</v>
-      </c>
-      <c r="AB40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3">
+        <v>11</v>
+      </c>
+      <c r="AA40" s="3">
+        <v>8.2462112512353212</v>
+      </c>
+      <c r="AB40" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>40</v>
       </c>
@@ -3915,22 +4018,23 @@
       </c>
       <c r="W41">
         <f>SQRT(POWER(L$8-B41,2)+POWER(M$8-C41,2))</f>
-        <v>9.8488578017961039</v>
+        <v>1.4142135623730951</v>
       </c>
       <c r="X41">
         <v>0</v>
       </c>
-      <c r="Z41">
-        <v>96</v>
-      </c>
-      <c r="AA41">
-        <v>9.0553851381374173</v>
-      </c>
-      <c r="AB41">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3">
+        <v>38</v>
+      </c>
+      <c r="AA41" s="3">
+        <v>8.5440037453175304</v>
+      </c>
+      <c r="AB41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC41" s="3"/>
+    </row>
+    <row r="42" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>41</v>
       </c>
@@ -3948,22 +4052,23 @@
       </c>
       <c r="W42">
         <f>SQRT(POWER(L$8-B42,2)+POWER(M$8-C42,2))</f>
-        <v>7.0710678118654755</v>
+        <v>9.2195444572928871</v>
       </c>
       <c r="X42">
         <v>0</v>
       </c>
-      <c r="Z42">
-        <v>4</v>
-      </c>
-      <c r="AA42">
+      <c r="Z42" s="3">
+        <v>41</v>
+      </c>
+      <c r="AA42" s="3">
         <v>9.2195444572928871</v>
       </c>
-      <c r="AB42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="3"/>
+    </row>
+    <row r="43" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>42</v>
       </c>
@@ -3981,22 +4086,23 @@
       </c>
       <c r="W43">
         <f>SQRT(POWER(L$8-B43,2)+POWER(M$8-C43,2))</f>
-        <v>10.63014581273465</v>
+        <v>4.2426406871192848</v>
       </c>
       <c r="X43">
         <v>0</v>
       </c>
-      <c r="Z43">
-        <v>20</v>
-      </c>
-      <c r="AA43">
+      <c r="Z43" s="3">
+        <v>49</v>
+      </c>
+      <c r="AA43" s="3">
         <v>9.2195444572928871</v>
       </c>
-      <c r="AB43">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC43" s="3"/>
+    </row>
+    <row r="44" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>43</v>
       </c>
@@ -4014,22 +4120,23 @@
       </c>
       <c r="W44">
         <f>SQRT(POWER(L$8-B44,2)+POWER(M$8-C44,2))</f>
-        <v>7.6157731058639087</v>
+        <v>7.2801098892805181</v>
       </c>
       <c r="X44">
         <v>0</v>
       </c>
-      <c r="Z44">
-        <v>39</v>
-      </c>
-      <c r="AA44">
+      <c r="Z44" s="3">
+        <v>29</v>
+      </c>
+      <c r="AA44" s="3">
         <v>9.4868329805051381</v>
       </c>
-      <c r="AB44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC44" s="3"/>
+    </row>
+    <row r="45" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>44</v>
       </c>
@@ -4047,22 +4154,23 @@
       </c>
       <c r="W45">
         <f>SQRT(POWER(L$8-B45,2)+POWER(M$8-C45,2))</f>
-        <v>7.2111025509279782</v>
+        <v>4.1231056256176606</v>
       </c>
       <c r="X45">
         <v>0</v>
       </c>
-      <c r="Z45">
-        <v>40</v>
-      </c>
-      <c r="AA45">
-        <v>9.8488578017961039</v>
-      </c>
-      <c r="AB45">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3">
+        <v>6</v>
+      </c>
+      <c r="AA45" s="3">
+        <v>10</v>
+      </c>
+      <c r="AB45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC45" s="3"/>
+    </row>
+    <row r="46" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>45</v>
       </c>
@@ -4080,22 +4188,23 @@
       </c>
       <c r="W46">
         <f>SQRT(POWER(L$8-B46,2)+POWER(M$8-C46,2))</f>
-        <v>7.6157731058639087</v>
+        <v>3.6055512754639891</v>
       </c>
       <c r="X46">
         <v>0</v>
       </c>
-      <c r="Z46">
-        <v>36</v>
-      </c>
-      <c r="AA46">
+      <c r="Z46" s="3">
         <v>10</v>
       </c>
-      <c r="AB46">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3">
+        <v>10.04987562112089</v>
+      </c>
+      <c r="AB46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC46" s="3"/>
+    </row>
+    <row r="47" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>46</v>
       </c>
@@ -4113,22 +4222,23 @@
       </c>
       <c r="W47">
         <f>SQRT(POWER(L$8-B47,2)+POWER(M$8-C47,2))</f>
-        <v>11.661903789690601</v>
+        <v>1</v>
       </c>
       <c r="X47">
         <v>0</v>
       </c>
-      <c r="Z47">
-        <v>79</v>
-      </c>
-      <c r="AA47">
-        <v>10</v>
-      </c>
-      <c r="AB47">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3">
+        <v>21</v>
+      </c>
+      <c r="AA47" s="3">
+        <v>10.198039027185569</v>
+      </c>
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC47" s="3"/>
+    </row>
+    <row r="48" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>47</v>
       </c>
@@ -4146,22 +4256,23 @@
       </c>
       <c r="W48">
         <f>SQRT(POWER(L$8-B48,2)+POWER(M$8-C48,2))</f>
-        <v>5.3851648071345037</v>
+        <v>8</v>
       </c>
       <c r="X48">
         <v>0</v>
       </c>
-      <c r="Z48">
-        <v>99</v>
-      </c>
-      <c r="AA48">
-        <v>10</v>
-      </c>
-      <c r="AB48">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3">
+        <v>34</v>
+      </c>
+      <c r="AA48" s="3">
+        <v>10.770329614269007</v>
+      </c>
+      <c r="AB48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC48" s="3"/>
+    </row>
+    <row r="49" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>48</v>
       </c>
@@ -4179,22 +4290,23 @@
       </c>
       <c r="W49">
         <f>SQRT(POWER(L$8-B49,2)+POWER(M$8-C49,2))</f>
-        <v>8</v>
+        <v>5.3851648071345037</v>
       </c>
       <c r="X49">
         <v>0</v>
       </c>
-      <c r="Z49">
-        <v>42</v>
-      </c>
-      <c r="AA49">
-        <v>10.63014581273465</v>
-      </c>
-      <c r="AB49">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3">
+        <v>77</v>
+      </c>
+      <c r="AA49" s="3">
+        <v>10.770329614269007</v>
+      </c>
+      <c r="AB49" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC49" s="3"/>
+    </row>
+    <row r="50" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>49</v>
       </c>
@@ -4212,22 +4324,23 @@
       </c>
       <c r="W50">
         <f>SQRT(POWER(L$8-B50,2)+POWER(M$8-C50,2))</f>
-        <v>7.0710678118654755</v>
+        <v>9.2195444572928871</v>
       </c>
       <c r="X50">
         <v>0</v>
       </c>
-      <c r="Z50">
-        <v>81</v>
-      </c>
-      <c r="AA50">
-        <v>11.045361017187261</v>
-      </c>
-      <c r="AB50">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>1</v>
+      </c>
+      <c r="AA50" s="3">
+        <v>11.180339887498949</v>
+      </c>
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC50" s="3"/>
+    </row>
+    <row r="51" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>50</v>
       </c>
@@ -4245,22 +4358,23 @@
       </c>
       <c r="W51">
         <f>SQRT(POWER(L$8-B51,2)+POWER(M$8-C51,2))</f>
-        <v>8.6023252670426267</v>
+        <v>3</v>
       </c>
       <c r="X51">
         <v>0</v>
       </c>
-      <c r="Z51">
-        <v>14</v>
-      </c>
-      <c r="AA51">
+      <c r="Z51" s="3">
+        <v>3</v>
+      </c>
+      <c r="AA51" s="3">
         <v>11.180339887498949</v>
       </c>
-      <c r="AB51">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC51" s="3"/>
+    </row>
+    <row r="52" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>51</v>
       </c>
@@ -4278,22 +4392,23 @@
       </c>
       <c r="W52">
         <f>SQRT(POWER(L$8-B52,2)+POWER(M$8-C52,2))</f>
-        <v>13.152946437965905</v>
+        <v>14.422205101855956</v>
       </c>
       <c r="X52">
         <v>1</v>
       </c>
-      <c r="Z52">
-        <v>17</v>
-      </c>
-      <c r="AA52">
+      <c r="Z52" s="3">
+        <v>22</v>
+      </c>
+      <c r="AA52" s="3">
         <v>11.180339887498949</v>
       </c>
-      <c r="AB52">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC52" s="3"/>
+    </row>
+    <row r="53" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>52</v>
       </c>
@@ -4311,22 +4426,23 @@
       </c>
       <c r="W53">
         <f>SQRT(POWER(L$8-B53,2)+POWER(M$8-C53,2))</f>
-        <v>21.470910553583888</v>
+        <v>24.413111231467404</v>
       </c>
       <c r="X53">
         <v>1</v>
       </c>
-      <c r="Z53">
-        <v>53</v>
-      </c>
-      <c r="AA53">
+      <c r="Z53" s="3">
+        <v>79</v>
+      </c>
+      <c r="AA53" s="3">
         <v>11.180339887498949</v>
       </c>
-      <c r="AB53">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC53" s="3"/>
+    </row>
+    <row r="54" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>53</v>
       </c>
@@ -4344,22 +4460,23 @@
       </c>
       <c r="W54">
         <f>SQRT(POWER(L$8-B54,2)+POWER(M$8-C54,2))</f>
+        <v>13.416407864998739</v>
+      </c>
+      <c r="X54">
+        <v>1</v>
+      </c>
+      <c r="Z54" s="3">
+        <v>99</v>
+      </c>
+      <c r="AA54" s="3">
         <v>11.180339887498949</v>
       </c>
-      <c r="X54">
-        <v>1</v>
-      </c>
-      <c r="Z54">
-        <v>37</v>
-      </c>
-      <c r="AA54">
-        <v>11.313708498984761</v>
-      </c>
-      <c r="AB54">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC54" s="3"/>
+    </row>
+    <row r="55" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>54</v>
       </c>
@@ -4377,22 +4494,23 @@
       </c>
       <c r="W55">
         <f>SQRT(POWER(L$8-B55,2)+POWER(M$8-C55,2))</f>
-        <v>16.763054614240211</v>
+        <v>18.601075237738275</v>
       </c>
       <c r="X55">
         <v>1</v>
       </c>
-      <c r="Z55">
-        <v>90</v>
-      </c>
-      <c r="AA55">
-        <v>11.401754250991379</v>
-      </c>
-      <c r="AB55">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3">
+        <v>96</v>
+      </c>
+      <c r="AA55" s="3">
+        <v>11.704699910719626</v>
+      </c>
+      <c r="AB55" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>55</v>
       </c>
@@ -4410,22 +4528,23 @@
       </c>
       <c r="W56">
         <f>SQRT(POWER(L$8-B56,2)+POWER(M$8-C56,2))</f>
-        <v>15.231546211727817</v>
+        <v>18.357559750685819</v>
       </c>
       <c r="X56">
         <v>1</v>
       </c>
-      <c r="Z56">
-        <v>46</v>
-      </c>
-      <c r="AA56">
-        <v>11.661903789690601</v>
-      </c>
-      <c r="AB56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3">
+        <v>56</v>
+      </c>
+      <c r="AA56" s="3">
+        <v>12.206555615733702</v>
+      </c>
+      <c r="AB56" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>56</v>
       </c>
@@ -4443,22 +4562,23 @@
       </c>
       <c r="W57">
         <f>SQRT(POWER(L$8-B57,2)+POWER(M$8-C57,2))</f>
-        <v>12</v>
+        <v>12.206555615733702</v>
       </c>
       <c r="X57">
         <v>1</v>
       </c>
-      <c r="Z57">
-        <v>76</v>
-      </c>
-      <c r="AA57">
-        <v>11.661903789690601</v>
-      </c>
-      <c r="AB57">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3">
+        <v>81</v>
+      </c>
+      <c r="AA57" s="3">
+        <v>12.529964086141668</v>
+      </c>
+      <c r="AB57" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC57" s="3"/>
+    </row>
+    <row r="58" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>57</v>
       </c>
@@ -4476,22 +4596,23 @@
       </c>
       <c r="W58">
         <f>SQRT(POWER(L$8-B58,2)+POWER(M$8-C58,2))</f>
-        <v>17</v>
+        <v>15.620499351813308</v>
       </c>
       <c r="X58">
         <v>1</v>
       </c>
-      <c r="Z58">
-        <v>56</v>
-      </c>
-      <c r="AA58">
-        <v>12</v>
-      </c>
-      <c r="AB58">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3">
+        <v>59</v>
+      </c>
+      <c r="AA58" s="3">
+        <v>13.038404810405298</v>
+      </c>
+      <c r="AB58" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC58" s="3"/>
+    </row>
+    <row r="59" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>58</v>
       </c>
@@ -4509,22 +4630,23 @@
       </c>
       <c r="W59">
         <f>SQRT(POWER(L$8-B59,2)+POWER(M$8-C59,2))</f>
-        <v>14.866068747318506</v>
+        <v>17.4928556845359</v>
       </c>
       <c r="X59">
         <v>1</v>
       </c>
-      <c r="Z59">
-        <v>7</v>
-      </c>
-      <c r="AA59">
-        <v>12.041594578792296</v>
-      </c>
-      <c r="AB59">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3">
+        <v>53</v>
+      </c>
+      <c r="AA59" s="3">
+        <v>13.416407864998739</v>
+      </c>
+      <c r="AB59" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC59" s="3"/>
+    </row>
+    <row r="60" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>59</v>
       </c>
@@ -4542,22 +4664,23 @@
       </c>
       <c r="W60">
         <f>SQRT(POWER(L$8-B60,2)+POWER(M$8-C60,2))</f>
-        <v>12.041594578792296</v>
+        <v>13.038404810405298</v>
       </c>
       <c r="X60">
         <v>1</v>
       </c>
-      <c r="Z60">
-        <v>59</v>
-      </c>
-      <c r="AA60">
-        <v>12.041594578792296</v>
-      </c>
-      <c r="AB60">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3">
+        <v>80</v>
+      </c>
+      <c r="AA60" s="3">
+        <v>14.212670403551895</v>
+      </c>
+      <c r="AB60" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC60" s="3"/>
+    </row>
+    <row r="61" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>60</v>
       </c>
@@ -4575,22 +4698,23 @@
       </c>
       <c r="W61">
         <f>SQRT(POWER(L$8-B61,2)+POWER(M$8-C61,2))</f>
-        <v>14.7648230602334</v>
+        <v>18.788294228055936</v>
       </c>
       <c r="X61">
         <v>1</v>
       </c>
-      <c r="Z61">
-        <v>16</v>
-      </c>
-      <c r="AA61">
-        <v>12.206555615733702</v>
-      </c>
-      <c r="AB61">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>90</v>
+      </c>
+      <c r="AA61" s="3">
+        <v>14.317821063276353</v>
+      </c>
+      <c r="AB61" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC61" s="3"/>
+    </row>
+    <row r="62" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>61</v>
       </c>
@@ -4608,22 +4732,23 @@
       </c>
       <c r="W62">
         <f>SQRT(POWER(L$8-B62,2)+POWER(M$8-C62,2))</f>
-        <v>17.4928556845359</v>
+        <v>21.470910553583888</v>
       </c>
       <c r="X62">
         <v>1</v>
       </c>
-      <c r="Z62">
-        <v>62</v>
-      </c>
-      <c r="AA62">
-        <v>12.529964086141668</v>
-      </c>
-      <c r="AB62">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3">
+        <v>51</v>
+      </c>
+      <c r="AA62" s="3">
+        <v>14.422205101855956</v>
+      </c>
+      <c r="AB62" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC62" s="3"/>
+    </row>
+    <row r="63" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>62</v>
       </c>
@@ -4641,22 +4766,23 @@
       </c>
       <c r="W63">
         <f>SQRT(POWER(L$8-B63,2)+POWER(M$8-C63,2))</f>
-        <v>12.529964086141668</v>
+        <v>17.088007490635061</v>
       </c>
       <c r="X63">
         <v>1</v>
       </c>
-      <c r="Z63">
-        <v>98</v>
-      </c>
-      <c r="AA63">
-        <v>12.649110640673518</v>
-      </c>
-      <c r="AB63">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>67</v>
+      </c>
+      <c r="AA63" s="3">
+        <v>15.556349186104045</v>
+      </c>
+      <c r="AB63" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC63" s="3"/>
+    </row>
+    <row r="64" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>63</v>
       </c>
@@ -4674,22 +4800,23 @@
       </c>
       <c r="W64">
         <f>SQRT(POWER(L$8-B64,2)+POWER(M$8-C64,2))</f>
-        <v>18.867962264113206</v>
+        <v>22.825424421026653</v>
       </c>
       <c r="X64">
         <v>1</v>
       </c>
-      <c r="Z64">
-        <v>68</v>
-      </c>
-      <c r="AA64">
-        <v>13.038404810405298</v>
-      </c>
-      <c r="AB64">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>57</v>
+      </c>
+      <c r="AA64" s="3">
+        <v>15.620499351813308</v>
+      </c>
+      <c r="AB64" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC64" s="3"/>
+    </row>
+    <row r="65" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>64</v>
       </c>
@@ -4707,22 +4834,23 @@
       </c>
       <c r="W65">
         <f>SQRT(POWER(L$8-B65,2)+POWER(M$8-C65,2))</f>
-        <v>14.422205101855956</v>
+        <v>19.313207915827967</v>
       </c>
       <c r="X65">
         <v>1</v>
       </c>
-      <c r="Z65">
-        <v>51</v>
-      </c>
-      <c r="AA65">
-        <v>13.152946437965905</v>
-      </c>
-      <c r="AB65">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>70</v>
+      </c>
+      <c r="AA65" s="3">
+        <v>15.620499351813308</v>
+      </c>
+      <c r="AB65" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC65" s="3"/>
+    </row>
+    <row r="66" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>65</v>
       </c>
@@ -4740,22 +4868,23 @@
       </c>
       <c r="W66">
         <f>SQRT(POWER(L$8-B66,2)+POWER(M$8-C66,2))</f>
-        <v>15.264337522473747</v>
+        <v>19.697715603592208</v>
       </c>
       <c r="X66">
         <v>1</v>
       </c>
-      <c r="Z66">
-        <v>92</v>
-      </c>
-      <c r="AA66">
-        <v>13.45362404707371</v>
-      </c>
-      <c r="AB66">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3">
+        <v>98</v>
+      </c>
+      <c r="AA66" s="3">
+        <v>15.652475842498529</v>
+      </c>
+      <c r="AB66" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC66" s="3"/>
+    </row>
+    <row r="67" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>66</v>
       </c>
@@ -4773,22 +4902,23 @@
       </c>
       <c r="W67">
         <f>SQRT(POWER(L$8-B67,2)+POWER(M$8-C67,2))</f>
-        <v>18.357559750685819</v>
+        <v>21.95449840010015</v>
       </c>
       <c r="X67">
         <v>1</v>
       </c>
-      <c r="Z67">
-        <v>80</v>
-      </c>
-      <c r="AA67">
-        <v>14.035668847618199</v>
-      </c>
-      <c r="AB67">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3">
+        <v>74</v>
+      </c>
+      <c r="AA67" s="3">
+        <v>16.278820596099706</v>
+      </c>
+      <c r="AB67" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>67</v>
       </c>
@@ -4806,22 +4936,23 @@
       </c>
       <c r="W68">
         <f>SQRT(POWER(L$8-B68,2)+POWER(M$8-C68,2))</f>
-        <v>16.031219541881399</v>
+        <v>15.556349186104045</v>
       </c>
       <c r="X68">
         <v>1</v>
       </c>
-      <c r="Z68">
-        <v>97</v>
-      </c>
-      <c r="AA68">
-        <v>14.317821063276353</v>
-      </c>
-      <c r="AB68">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>83</v>
+      </c>
+      <c r="AA68" s="3">
+        <v>16.278820596099706</v>
+      </c>
+      <c r="AB68" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC68" s="3"/>
+    </row>
+    <row r="69" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>68</v>
       </c>
@@ -4839,22 +4970,23 @@
       </c>
       <c r="W69">
         <f>SQRT(POWER(L$8-B69,2)+POWER(M$8-C69,2))</f>
-        <v>13.038404810405298</v>
+        <v>18.027756377319946</v>
       </c>
       <c r="X69">
         <v>1</v>
       </c>
-      <c r="Z69">
-        <v>64</v>
-      </c>
-      <c r="AA69">
-        <v>14.422205101855956</v>
-      </c>
-      <c r="AB69">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>86</v>
+      </c>
+      <c r="AA69" s="3">
+        <v>16.643316977093239</v>
+      </c>
+      <c r="AB69" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC69" s="3"/>
+    </row>
+    <row r="70" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>69</v>
       </c>
@@ -4872,22 +5004,23 @@
       </c>
       <c r="W70">
         <f>SQRT(POWER(L$8-B70,2)+POWER(M$8-C70,2))</f>
-        <v>20.248456731316587</v>
+        <v>22.022715545545239</v>
       </c>
       <c r="X70">
         <v>1</v>
       </c>
-      <c r="Z70">
-        <v>86</v>
-      </c>
-      <c r="AA70">
-        <v>14.560219778561036</v>
-      </c>
-      <c r="AB70">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="71" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>76</v>
+      </c>
+      <c r="AA70" s="3">
+        <v>16.763054614240211</v>
+      </c>
+      <c r="AB70" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC70" s="3"/>
+    </row>
+    <row r="71" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>70</v>
       </c>
@@ -4905,22 +5038,23 @@
       </c>
       <c r="W71">
         <f>SQRT(POWER(L$8-B71,2)+POWER(M$8-C71,2))</f>
-        <v>15.132745950421556</v>
+        <v>15.620499351813308</v>
       </c>
       <c r="X71">
         <v>1</v>
       </c>
-      <c r="Z71">
-        <v>60</v>
-      </c>
-      <c r="AA71">
-        <v>14.7648230602334</v>
-      </c>
-      <c r="AB71">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>62</v>
+      </c>
+      <c r="AA71" s="3">
+        <v>17.088007490635061</v>
+      </c>
+      <c r="AB71" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC71" s="3"/>
+    </row>
+    <row r="72" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>71</v>
       </c>
@@ -4938,22 +5072,23 @@
       </c>
       <c r="W72">
         <f>SQRT(POWER(L$8-B72,2)+POWER(M$8-C72,2))</f>
-        <v>17</v>
+        <v>20.591260281974002</v>
       </c>
       <c r="X72">
         <v>1</v>
       </c>
-      <c r="Z72">
+      <c r="Z72" s="3">
         <v>58</v>
       </c>
-      <c r="AA72">
-        <v>14.866068747318506</v>
-      </c>
-      <c r="AB72">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3">
+        <v>17.4928556845359</v>
+      </c>
+      <c r="AB72" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC72" s="3"/>
+    </row>
+    <row r="73" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>72</v>
       </c>
@@ -4971,22 +5106,23 @@
       </c>
       <c r="W73">
         <f>SQRT(POWER(L$8-B73,2)+POWER(M$8-C73,2))</f>
-        <v>18.681541692269406</v>
+        <v>19.849433241279208</v>
       </c>
       <c r="X73">
         <v>1</v>
       </c>
-      <c r="Z73">
-        <v>70</v>
-      </c>
-      <c r="AA73">
-        <v>15.132745950421556</v>
-      </c>
-      <c r="AB73">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>97</v>
+      </c>
+      <c r="AA73" s="3">
+        <v>17.888543819998318</v>
+      </c>
+      <c r="AB73" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC73" s="3"/>
+    </row>
+    <row r="74" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>73</v>
       </c>
@@ -5004,22 +5140,23 @@
       </c>
       <c r="W74">
         <f>SQRT(POWER(L$8-B74,2)+POWER(M$8-C74,2))</f>
+        <v>20</v>
+      </c>
+      <c r="X74">
+        <v>1</v>
+      </c>
+      <c r="Z74" s="3">
+        <v>68</v>
+      </c>
+      <c r="AA74" s="3">
         <v>18.027756377319946</v>
       </c>
-      <c r="X74">
-        <v>1</v>
-      </c>
-      <c r="Z74">
-        <v>55</v>
-      </c>
-      <c r="AA74">
-        <v>15.231546211727817</v>
-      </c>
-      <c r="AB74">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="75" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC74" s="3"/>
+    </row>
+    <row r="75" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>74</v>
       </c>
@@ -5037,22 +5174,23 @@
       </c>
       <c r="W75">
         <f>SQRT(POWER(L$8-B75,2)+POWER(M$8-C75,2))</f>
-        <v>16.124515496597098</v>
+        <v>16.278820596099706</v>
       </c>
       <c r="X75">
         <v>1</v>
       </c>
-      <c r="Z75">
-        <v>65</v>
-      </c>
-      <c r="AA75">
-        <v>15.264337522473747</v>
-      </c>
-      <c r="AB75">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>55</v>
+      </c>
+      <c r="AA75" s="3">
+        <v>18.357559750685819</v>
+      </c>
+      <c r="AB75" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC75" s="3"/>
+    </row>
+    <row r="76" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>75</v>
       </c>
@@ -5070,22 +5208,23 @@
       </c>
       <c r="W76">
         <f>SQRT(POWER(L$8-B76,2)+POWER(M$8-C76,2))</f>
-        <v>18.384776310850235</v>
+        <v>20.808652046684813</v>
       </c>
       <c r="X76">
         <v>1</v>
       </c>
-      <c r="Z76">
-        <v>93</v>
-      </c>
-      <c r="AA76">
-        <v>15.620499351813308</v>
-      </c>
-      <c r="AB76">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3">
+        <v>54</v>
+      </c>
+      <c r="AA76" s="3">
+        <v>18.601075237738275</v>
+      </c>
+      <c r="AB76" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC76" s="3"/>
+    </row>
+    <row r="77" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>76</v>
       </c>
@@ -5103,22 +5242,23 @@
       </c>
       <c r="W77">
         <f>SQRT(POWER(L$8-B77,2)+POWER(M$8-C77,2))</f>
-        <v>11.661903789690601</v>
+        <v>16.763054614240211</v>
       </c>
       <c r="X77">
         <v>1</v>
       </c>
-      <c r="Z77">
-        <v>67</v>
-      </c>
-      <c r="AA77">
-        <v>16.031219541881399</v>
-      </c>
-      <c r="AB77">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>60</v>
+      </c>
+      <c r="AA77" s="3">
+        <v>18.788294228055936</v>
+      </c>
+      <c r="AB77" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC77" s="3"/>
+    </row>
+    <row r="78" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>77</v>
       </c>
@@ -5136,22 +5276,23 @@
       </c>
       <c r="W78">
         <f>SQRT(POWER(L$8-B78,2)+POWER(M$8-C78,2))</f>
-        <v>9</v>
+        <v>10.770329614269007</v>
       </c>
       <c r="X78">
         <v>1</v>
       </c>
-      <c r="Z78">
-        <v>74</v>
-      </c>
-      <c r="AA78">
-        <v>16.124515496597098</v>
-      </c>
-      <c r="AB78">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="79" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z78" s="3">
+        <v>64</v>
+      </c>
+      <c r="AA78" s="3">
+        <v>19.313207915827967</v>
+      </c>
+      <c r="AB78" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC78" s="3"/>
+    </row>
+    <row r="79" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>78</v>
       </c>
@@ -5169,22 +5310,23 @@
       </c>
       <c r="W79">
         <f>SQRT(POWER(L$8-B79,2)+POWER(M$8-C79,2))</f>
-        <v>17.888543819998318</v>
+        <v>21.095023109728988</v>
       </c>
       <c r="X79">
         <v>1</v>
       </c>
-      <c r="Z79">
-        <v>83</v>
-      </c>
-      <c r="AA79">
-        <v>16.124515496597098</v>
-      </c>
-      <c r="AB79">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z79" s="3">
+        <v>84</v>
+      </c>
+      <c r="AA79" s="3">
+        <v>19.416487838947599</v>
+      </c>
+      <c r="AB79" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC79" s="3"/>
+    </row>
+    <row r="80" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>79</v>
       </c>
@@ -5202,22 +5344,23 @@
       </c>
       <c r="W80">
         <f>SQRT(POWER(L$8-B80,2)+POWER(M$8-C80,2))</f>
-        <v>10</v>
+        <v>11.180339887498949</v>
       </c>
       <c r="X80">
         <v>1</v>
       </c>
-      <c r="Z80">
-        <v>91</v>
-      </c>
-      <c r="AA80">
-        <v>16.643316977093239</v>
-      </c>
-      <c r="AB80">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="81" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z80" s="3">
+        <v>87</v>
+      </c>
+      <c r="AA80" s="3">
+        <v>19.416487838947599</v>
+      </c>
+      <c r="AB80" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC80" s="3"/>
+    </row>
+    <row r="81" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>80</v>
       </c>
@@ -5235,22 +5378,23 @@
       </c>
       <c r="W81">
         <f>SQRT(POWER(L$8-B81,2)+POWER(M$8-C81,2))</f>
-        <v>14.035668847618199</v>
+        <v>14.212670403551895</v>
       </c>
       <c r="X81">
         <v>1</v>
       </c>
-      <c r="Z81">
-        <v>54</v>
-      </c>
-      <c r="AA81">
-        <v>16.763054614240211</v>
-      </c>
-      <c r="AB81">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="82" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z81" s="3">
+        <v>65</v>
+      </c>
+      <c r="AA81" s="3">
+        <v>19.697715603592208</v>
+      </c>
+      <c r="AB81" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC81" s="3"/>
+    </row>
+    <row r="82" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>81</v>
       </c>
@@ -5268,22 +5412,23 @@
       </c>
       <c r="W82">
         <f>SQRT(POWER(L$8-B82,2)+POWER(M$8-C82,2))</f>
-        <v>11.045361017187261</v>
+        <v>12.529964086141668</v>
       </c>
       <c r="X82">
         <v>1</v>
       </c>
-      <c r="Z82">
-        <v>57</v>
-      </c>
-      <c r="AA82">
-        <v>17</v>
-      </c>
-      <c r="AB82">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="83" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3">
+        <v>72</v>
+      </c>
+      <c r="AA82" s="3">
+        <v>19.849433241279208</v>
+      </c>
+      <c r="AB82" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>82</v>
       </c>
@@ -5301,22 +5446,23 @@
       </c>
       <c r="W83">
         <f>SQRT(POWER(L$8-B83,2)+POWER(M$8-C83,2))</f>
-        <v>19.313207915827967</v>
+        <v>21.400934559032695</v>
       </c>
       <c r="X83">
         <v>1</v>
       </c>
-      <c r="Z83">
-        <v>71</v>
-      </c>
-      <c r="AA83">
-        <v>17</v>
-      </c>
-      <c r="AB83">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="84" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3">
+        <v>73</v>
+      </c>
+      <c r="AA83" s="3">
+        <v>20</v>
+      </c>
+      <c r="AB83" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC83" s="3"/>
+    </row>
+    <row r="84" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>83</v>
       </c>
@@ -5334,22 +5480,23 @@
       </c>
       <c r="W84">
         <f>SQRT(POWER(L$8-B84,2)+POWER(M$8-C84,2))</f>
-        <v>16.124515496597098</v>
+        <v>16.278820596099706</v>
       </c>
       <c r="X84">
         <v>1</v>
       </c>
-      <c r="Z84">
-        <v>84</v>
-      </c>
-      <c r="AA84">
-        <v>17.088007490635061</v>
-      </c>
-      <c r="AB84">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="85" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>92</v>
+      </c>
+      <c r="AA84" s="3">
+        <v>20.396078054371138</v>
+      </c>
+      <c r="AB84" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC84" s="3"/>
+    </row>
+    <row r="85" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>84</v>
       </c>
@@ -5367,22 +5514,23 @@
       </c>
       <c r="W85">
         <f>SQRT(POWER(L$8-B85,2)+POWER(M$8-C85,2))</f>
-        <v>17.088007490635061</v>
+        <v>19.416487838947599</v>
       </c>
       <c r="X85">
         <v>1</v>
       </c>
-      <c r="Z85">
-        <v>87</v>
-      </c>
-      <c r="AA85">
-        <v>17.088007490635061</v>
-      </c>
-      <c r="AB85">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="86" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>71</v>
+      </c>
+      <c r="AA85" s="3">
+        <v>20.591260281974002</v>
+      </c>
+      <c r="AB85" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC85" s="3"/>
+    </row>
+    <row r="86" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>85</v>
       </c>
@@ -5400,22 +5548,23 @@
       </c>
       <c r="W86">
         <f>SQRT(POWER(L$8-B86,2)+POWER(M$8-C86,2))</f>
-        <v>18.384776310850235</v>
+        <v>20.808652046684813</v>
       </c>
       <c r="X86">
         <v>1</v>
       </c>
-      <c r="Z86">
-        <v>88</v>
-      </c>
-      <c r="AA86">
-        <v>17.204650534085253</v>
-      </c>
-      <c r="AB86">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="87" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>75</v>
+      </c>
+      <c r="AA86" s="3">
+        <v>20.808652046684813</v>
+      </c>
+      <c r="AB86" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC86" s="3"/>
+    </row>
+    <row r="87" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>86</v>
       </c>
@@ -5433,22 +5582,23 @@
       </c>
       <c r="W87">
         <f>SQRT(POWER(L$8-B87,2)+POWER(M$8-C87,2))</f>
-        <v>14.560219778561036</v>
+        <v>16.643316977093239</v>
       </c>
       <c r="X87">
         <v>1</v>
       </c>
-      <c r="Z87">
-        <v>61</v>
-      </c>
-      <c r="AA87">
-        <v>17.4928556845359</v>
-      </c>
-      <c r="AB87">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="88" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>85</v>
+      </c>
+      <c r="AA87" s="3">
+        <v>20.808652046684813</v>
+      </c>
+      <c r="AB87" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC87" s="3"/>
+    </row>
+    <row r="88" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>87</v>
       </c>
@@ -5466,22 +5616,23 @@
       </c>
       <c r="W88">
         <f>SQRT(POWER(L$8-B88,2)+POWER(M$8-C88,2))</f>
-        <v>17.088007490635061</v>
+        <v>19.416487838947599</v>
       </c>
       <c r="X88">
         <v>1</v>
       </c>
-      <c r="Z88">
-        <v>78</v>
-      </c>
-      <c r="AA88">
-        <v>17.888543819998318</v>
-      </c>
-      <c r="AB88">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="89" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>91</v>
+      </c>
+      <c r="AA88" s="3">
+        <v>21.023796041628639</v>
+      </c>
+      <c r="AB88" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC88" s="3"/>
+    </row>
+    <row r="89" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>88</v>
       </c>
@@ -5499,22 +5650,23 @@
       </c>
       <c r="W89">
         <f>SQRT(POWER(L$8-B89,2)+POWER(M$8-C89,2))</f>
-        <v>17.204650534085253</v>
+        <v>21.931712199461309</v>
       </c>
       <c r="X89">
         <v>1</v>
       </c>
-      <c r="Z89">
-        <v>73</v>
-      </c>
-      <c r="AA89">
-        <v>18.027756377319946</v>
-      </c>
-      <c r="AB89">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="90" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3">
+        <v>78</v>
+      </c>
+      <c r="AA89" s="3">
+        <v>21.095023109728988</v>
+      </c>
+      <c r="AB89" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC89" s="3"/>
+    </row>
+    <row r="90" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>89</v>
       </c>
@@ -5532,22 +5684,23 @@
       </c>
       <c r="W90">
         <f>SQRT(POWER(L$8-B90,2)+POWER(M$8-C90,2))</f>
-        <v>18.788294228055936</v>
+        <v>21.633307652783937</v>
       </c>
       <c r="X90">
         <v>1</v>
       </c>
-      <c r="Z90">
-        <v>66</v>
-      </c>
-      <c r="AA90">
-        <v>18.357559750685819</v>
-      </c>
-      <c r="AB90">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="91" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3">
+        <v>93</v>
+      </c>
+      <c r="AA90" s="3">
+        <v>21.189620100417091</v>
+      </c>
+      <c r="AB90" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>90</v>
       </c>
@@ -5565,22 +5718,23 @@
       </c>
       <c r="W91">
         <f>SQRT(POWER(L$8-B91,2)+POWER(M$8-C91,2))</f>
-        <v>11.401754250991379</v>
+        <v>14.317821063276353</v>
       </c>
       <c r="X91">
         <v>1</v>
       </c>
-      <c r="Z91">
-        <v>75</v>
-      </c>
-      <c r="AA91">
-        <v>18.384776310850235</v>
-      </c>
-      <c r="AB91">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="92" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3">
+        <v>82</v>
+      </c>
+      <c r="AA91" s="3">
+        <v>21.400934559032695</v>
+      </c>
+      <c r="AB91" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC91" s="3"/>
+    </row>
+    <row r="92" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>91</v>
       </c>
@@ -5598,22 +5752,23 @@
       </c>
       <c r="W92">
         <f>SQRT(POWER(L$8-B92,2)+POWER(M$8-C92,2))</f>
-        <v>16.643316977093239</v>
+        <v>21.023796041628639</v>
       </c>
       <c r="X92">
         <v>1</v>
       </c>
-      <c r="Z92">
-        <v>85</v>
-      </c>
-      <c r="AA92">
-        <v>18.384776310850235</v>
-      </c>
-      <c r="AB92">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="93" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>61</v>
+      </c>
+      <c r="AA92" s="3">
+        <v>21.470910553583888</v>
+      </c>
+      <c r="AB92" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC92" s="3"/>
+    </row>
+    <row r="93" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>92</v>
       </c>
@@ -5631,22 +5786,23 @@
       </c>
       <c r="W93">
         <f>SQRT(POWER(L$8-B93,2)+POWER(M$8-C93,2))</f>
-        <v>13.45362404707371</v>
+        <v>20.396078054371138</v>
       </c>
       <c r="X93">
         <v>1</v>
       </c>
-      <c r="Z93">
-        <v>72</v>
-      </c>
-      <c r="AA93">
-        <v>18.681541692269406</v>
-      </c>
-      <c r="AB93">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="94" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>89</v>
+      </c>
+      <c r="AA93" s="3">
+        <v>21.633307652783937</v>
+      </c>
+      <c r="AB93" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC93" s="3"/>
+    </row>
+    <row r="94" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>93</v>
       </c>
@@ -5664,22 +5820,23 @@
       </c>
       <c r="W94">
         <f>SQRT(POWER(L$8-B94,2)+POWER(M$8-C94,2))</f>
-        <v>15.620499351813308</v>
+        <v>21.189620100417091</v>
       </c>
       <c r="X94">
         <v>1</v>
       </c>
-      <c r="Z94">
-        <v>89</v>
-      </c>
-      <c r="AA94">
-        <v>18.788294228055936</v>
-      </c>
-      <c r="AB94">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="95" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3">
+        <v>88</v>
+      </c>
+      <c r="AA94" s="3">
+        <v>21.931712199461309</v>
+      </c>
+      <c r="AB94" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC94" s="3"/>
+    </row>
+    <row r="95" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>94</v>
       </c>
@@ -5697,22 +5854,23 @@
       </c>
       <c r="W95">
         <f>SQRT(POWER(L$8-B95,2)+POWER(M$8-C95,2))</f>
-        <v>20.124611797498108</v>
+        <v>23.021728866442675</v>
       </c>
       <c r="X95">
         <v>1</v>
       </c>
-      <c r="Z95">
-        <v>63</v>
-      </c>
-      <c r="AA95">
-        <v>18.867962264113206</v>
-      </c>
-      <c r="AB95">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="96" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3">
+        <v>66</v>
+      </c>
+      <c r="AA95" s="3">
+        <v>21.95449840010015</v>
+      </c>
+      <c r="AB95" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>95</v>
       </c>
@@ -5730,22 +5888,23 @@
       </c>
       <c r="W96">
         <f>SQRT(POWER(L$8-B96,2)+POWER(M$8-C96,2))</f>
-        <v>20.248456731316587</v>
+        <v>22.022715545545239</v>
       </c>
       <c r="X96">
         <v>1</v>
       </c>
-      <c r="Z96">
-        <v>82</v>
-      </c>
-      <c r="AA96">
-        <v>19.313207915827967</v>
-      </c>
-      <c r="AB96">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="97" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>69</v>
+      </c>
+      <c r="AA96" s="3">
+        <v>22.022715545545239</v>
+      </c>
+      <c r="AB96" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC96" s="3"/>
+    </row>
+    <row r="97" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>96</v>
       </c>
@@ -5763,22 +5922,23 @@
       </c>
       <c r="W97">
         <f>SQRT(POWER(L$8-B97,2)+POWER(M$8-C97,2))</f>
-        <v>9.0553851381374173</v>
+        <v>11.704699910719626</v>
       </c>
       <c r="X97">
         <v>1</v>
       </c>
-      <c r="Z97">
-        <v>100</v>
-      </c>
-      <c r="AA97">
-        <v>19.697715603592208</v>
-      </c>
-      <c r="AB97">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="98" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>95</v>
+      </c>
+      <c r="AA97" s="3">
+        <v>22.022715545545239</v>
+      </c>
+      <c r="AB97" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC97" s="3"/>
+    </row>
+    <row r="98" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>97</v>
       </c>
@@ -5796,22 +5956,23 @@
       </c>
       <c r="W98">
         <f>SQRT(POWER(L$8-B98,2)+POWER(M$8-C98,2))</f>
-        <v>14.317821063276353</v>
+        <v>17.888543819998318</v>
       </c>
       <c r="X98">
         <v>1</v>
       </c>
-      <c r="Z98">
-        <v>94</v>
-      </c>
-      <c r="AA98">
-        <v>20.124611797498108</v>
-      </c>
-      <c r="AB98">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="99" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA98" s="3">
+        <v>22.203603311174518</v>
+      </c>
+      <c r="AB98" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC98" s="3"/>
+    </row>
+    <row r="99" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>98</v>
       </c>
@@ -5829,22 +5990,23 @@
       </c>
       <c r="W99">
         <f>SQRT(POWER(L$8-B99,2)+POWER(M$8-C99,2))</f>
-        <v>12.649110640673518</v>
+        <v>15.652475842498529</v>
       </c>
       <c r="X99">
         <v>1</v>
       </c>
-      <c r="Z99">
-        <v>69</v>
-      </c>
-      <c r="AA99">
-        <v>20.248456731316587</v>
-      </c>
-      <c r="AB99">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="100" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>63</v>
+      </c>
+      <c r="AA99" s="3">
+        <v>22.825424421026653</v>
+      </c>
+      <c r="AB99" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC99" s="3"/>
+    </row>
+    <row r="100" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>99</v>
       </c>
@@ -5862,22 +6024,23 @@
       </c>
       <c r="W100">
         <f>SQRT(POWER(L$8-B100,2)+POWER(M$8-C100,2))</f>
-        <v>10</v>
+        <v>11.180339887498949</v>
       </c>
       <c r="X100">
         <v>1</v>
       </c>
-      <c r="Z100">
-        <v>95</v>
-      </c>
-      <c r="AA100">
-        <v>20.248456731316587</v>
-      </c>
-      <c r="AB100">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="101" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3">
+        <v>94</v>
+      </c>
+      <c r="AA100" s="3">
+        <v>23.021728866442675</v>
+      </c>
+      <c r="AB100" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC100" s="3"/>
+    </row>
+    <row r="101" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>100</v>
       </c>
@@ -5895,20 +6058,21 @@
       </c>
       <c r="W101">
         <f>SQRT(POWER(L$8-B101,2)+POWER(M$8-C101,2))</f>
-        <v>19.697715603592208</v>
+        <v>22.203603311174518</v>
       </c>
       <c r="X101">
         <v>1</v>
       </c>
-      <c r="Z101">
+      <c r="Z101" s="3">
         <v>52</v>
       </c>
-      <c r="AA101">
-        <v>21.470910553583888</v>
-      </c>
-      <c r="AB101">
-        <v>1</v>
-      </c>
+      <c r="AA101" s="3">
+        <v>24.413111231467404</v>
+      </c>
+      <c r="AB101" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC101" s="3"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="Z2:AB101">
